--- a/Data/20251109_DB.xlsx
+++ b/Data/20251109_DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorgeviafara/Documents/Talleres_eva_impacto/Proyecto_Final_EIE/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202A5CAB-9964-1142-93B0-93B4B1A687D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E51AF29-188E-134A-9755-4D5D9C2F5111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="13900" xr2:uid="{4588459C-B41F-4963-AF95-24227B19DC6A}"/>
   </bookViews>
